--- a/data/fmsForecastOutput/File1/RPT_RPT6659694529226EG_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6659694529226EG_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>300.7409600791409</v>
+        <v>203.1406627850366</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>332.8206552358941</v>
+        <v>289.5414489036987</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>366.1755790260343</v>
+        <v>318.3454734885774</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>394.3661134487203</v>
+        <v>341.4322490025465</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>427.3040520808261</v>
+        <v>370.5112832573204</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>37.56934345616631</v>
+        <v>25.37686029889628</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>43.18617607186552</v>
+        <v>37.57034846168297</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>49.49052905518452</v>
+        <v>43.0260421712961</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>56.04289913634116</v>
+        <v>48.5205306445072</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>64.36174721438718</v>
+        <v>55.8074594354073</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>47424598.08329053</v>
+        <v>32033761.82751573</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>55410467.85654642</v>
+        <v>48205022.42039335</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>64457296.43036576</v>
+        <v>56037840.11620142</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>74042493.58908701</v>
+        <v>64104126.20598003</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>86570106.42502297</v>
+        <v>75064116.68006118</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>352.291852048476</v>
+        <v>237.9616009075151</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>389.8704220475512</v>
+        <v>339.1725997424519</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>428.9428113684871</v>
+        <v>372.914006848376</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>461.9655681602156</v>
+        <v>399.9581544147842</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>500.5494956714865</v>
+        <v>434.0217114064874</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.2698937985948</v>
+        <v>31.25379692465685</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.17241563229771</v>
+        <v>46.25800118377019</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>60.91527445543132</v>
+        <v>52.95847948347805</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>68.95211170070326</v>
+        <v>59.69700176713372</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>79.14764948921368</v>
+        <v>68.62817480022917</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>47424598.08329053</v>
+        <v>32033761.82751573</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>55410467.85654642</v>
+        <v>48205022.42039335</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>64457296.43036576</v>
+        <v>56037840.11620142</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>74042493.58908701</v>
+        <v>64104126.20598003</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>86570106.42502297</v>
+        <v>75064116.68006118</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>550.1991098219373</v>
+        <v>375.1385142805242</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>606.8032727787472</v>
+        <v>527.8958616163919</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>665.8009218871562</v>
+        <v>578.8333679221213</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>709.0525545580731</v>
+        <v>613.8797217681537</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>759.9475633607693</v>
+        <v>658.9431891584778</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>62.44396997308113</v>
+        <v>42.57574704012239</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>70.04254821614126</v>
+        <v>60.9343637371077</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>79.43263813965828</v>
+        <v>69.05707088388533</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>89.21944248917403</v>
+        <v>77.24393090396538</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>101.8920496610932</v>
+        <v>88.34961172406699</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>17686936.99423293</v>
+        <v>12059363.8698127</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>20003703.48836537</v>
+        <v>17402464.2948157</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>22877617.30630274</v>
+        <v>19889321.02693155</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>25913592.39658747</v>
+        <v>22435331.18690368</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>29941550.96793955</v>
+        <v>25962029.53255459</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>556.9930772043903</v>
+        <v>379.7707988197495</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>614.2961995560346</v>
+        <v>534.4144240806503</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>674.0223632994703</v>
+        <v>585.9809167845885</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>717.8080756814561</v>
+        <v>621.4600299365765</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>769.331546114792</v>
+        <v>667.0799499312844</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>62.72131460770862</v>
+        <v>42.76484704468528</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>70.35484150852272</v>
+        <v>61.20604707181318</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>79.78952239896928</v>
+        <v>69.367338579505</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>89.62545070962761</v>
+        <v>77.59544252578441</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>102.3631664549175</v>
+        <v>88.75811254380224</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>17686936.99423293</v>
+        <v>12059363.8698127</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>20003703.48836537</v>
+        <v>17402464.2948157</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>22877617.30630274</v>
+        <v>19889321.02693155</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>25913592.39658747</v>
+        <v>22435331.18690368</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>29941550.96793955</v>
+        <v>25962029.53255459</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>342.9830243778948</v>
+        <v>232.2659662061156</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>378.1046296252325</v>
+        <v>328.9367770368026</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>415.1107394508189</v>
+        <v>360.8886601933422</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>445.6407889586572</v>
+        <v>385.8245517351083</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>481.462022131731</v>
+        <v>417.4711246244776</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>42.12793791789213</v>
+        <v>28.52877696357821</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>48.07572374059487</v>
+        <v>41.82406768363899</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>54.91278158565105</v>
+        <v>47.74003245532305</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>62.02199844996622</v>
+        <v>53.69708146687126</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>71.09090516440537</v>
+        <v>61.64224542187505</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>65111535.07752346</v>
+        <v>44093125.69732843</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>75414171.34491178</v>
+        <v>65607486.71520904</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>87334913.7366685</v>
+        <v>75927161.14313297</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>99956085.98567449</v>
+        <v>86539457.39288372</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>116511657.3929625</v>
+        <v>101026146.2126158</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>391.3618938429027</v>
+        <v>265.0278350497149</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>431.7054311111228</v>
+        <v>375.5674541190532</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>474.0998535894215</v>
+        <v>412.1725715554923</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>508.9981653037589</v>
+        <v>440.6777696925184</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>549.922945777186</v>
+        <v>476.8329381701342</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>49.81951886167651</v>
+        <v>33.73746763508004</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.8555793556645</v>
+        <v>49.46221115660307</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>64.93923638439674</v>
+        <v>56.45682413263675</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>73.33766865071324</v>
+        <v>63.49390323668142</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>84.04608084902668</v>
+        <v>72.87555462209015</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>65111535.07752346</v>
+        <v>44093125.69732843</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>75414171.34491178</v>
+        <v>65607486.71520904</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>87334913.7366685</v>
+        <v>75927161.14313297</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>99956085.98567449</v>
+        <v>86539457.39288372</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>116511657.3929625</v>
+        <v>101026146.2126158</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="AS10" s="154" t="n">
-        <v>0.980726167491445</v>
+        <v>0.7855555</v>
       </c>
       <c r="AT10" s="154" t="n">
         <v>0.9490429845289819</v>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>702.1079318055075</v>
+        <v>479.7508916801084</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>762.2386050884729</v>
+        <v>663.11876490906</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>824.7878903133742</v>
+        <v>717.0533898859611</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>874.1644087084682</v>
+        <v>756.8295275660017</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>928.448942169601</v>
+        <v>805.0492630476102</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>120.2709688986606</v>
+        <v>82.18124587196178</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>135.8075512270153</v>
+        <v>118.1474344566022</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>154.4106326223431</v>
+        <v>134.2413835807157</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>174.4523311576863</v>
+        <v>151.0364344024572</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>198.8771666116091</v>
+        <v>172.4445030262375</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>8225347.283844909</v>
+        <v>5620386.147263005</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>9454913.551621262</v>
+        <v>8225417.283798292</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>10954992.05560248</v>
+        <v>9524041.613485556</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>12634093.1797238</v>
+        <v>10938279.66133092</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>14786148.15626932</v>
+        <v>12820928.68639722</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>892.991300076529</v>
+        <v>610.181644540899</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>969.4698095435131</v>
+        <v>843.4020770261272</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1049.024483407125</v>
+        <v>912.0000071953663</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1111.825086216868</v>
+        <v>962.5901562164456</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1180.868055130275</v>
+        <v>1023.919479425111</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>138.863788892117</v>
+        <v>94.88573412317753</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>156.9221372500337</v>
+        <v>136.5163259187776</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>178.5973718321608</v>
+        <v>155.2688302059298</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>202.0565921774845</v>
+        <v>174.9355083275658</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>230.723276269995</v>
+        <v>200.0579623635993</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>8225347.283844909</v>
+        <v>5620386.147263005</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>9454913.551621262</v>
+        <v>8225417.283798292</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>10954992.05560248</v>
+        <v>9524041.613485556</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>12634093.1797238</v>
+        <v>10938279.66133092</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>14786148.15626932</v>
+        <v>12820928.68639722</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>363.8569495207902</v>
+        <v>246.6508827114696</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>400.5954795349118</v>
+        <v>348.502963346382</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>439.4384161359094</v>
+        <v>382.0386324882373</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>471.5815058937587</v>
+        <v>408.2833722434442</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>509.0617527638311</v>
+        <v>441.4025904903311</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>45.4391865398422</v>
+        <v>30.80225754792907</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>51.80396771401292</v>
+        <v>45.06749872064001</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>59.16172002266089</v>
+        <v>51.43397068434494</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>66.85700661818808</v>
+        <v>57.88310987396031</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>76.63628460615206</v>
+        <v>66.45059144013784</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>73336882.36136839</v>
+        <v>49713511.84459144</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>84869084.89653306</v>
+        <v>73832903.99900734</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>98289905.792271</v>
+        <v>85451202.75661851</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>112590179.1653983</v>
+        <v>97477737.05421463</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>131297805.5492318</v>
+        <v>113847074.899013</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>417.6771936160772</v>
+        <v>283.1344808159791</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>460.1406367978277</v>
+        <v>400.3050051046791</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>504.9439166498962</v>
+        <v>438.9877541805956</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>541.9725763321788</v>
+        <v>469.2261854268319</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>585.1309027967665</v>
+        <v>507.361424951251</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>53.68019002332776</v>
+        <v>36.38865842966863</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>61.20358017222154</v>
+        <v>53.24480716105586</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>69.89701636445884</v>
+        <v>60.76701436732605</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>78.98379982597974</v>
+        <v>68.38218153707068</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>90.52716552661221</v>
+        <v>78.49524179777018</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>73336882.36136839</v>
+        <v>49713511.84459144</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>84869084.89653306</v>
+        <v>73832903.99900734</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>98289905.792271</v>
+        <v>85451202.75661851</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>112590179.1653983</v>
+        <v>97477737.05421463</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>131297805.5492318</v>
+        <v>113847074.899013</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>3209.812768059381</v>
+        <v>2489.932521250425</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3305.9118784958</v>
+        <v>2829.88005752448</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3479.547699358201</v>
+        <v>2976.676003879859</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3625.884961160802</v>
+        <v>3088.071294818667</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3840.484076832168</v>
+        <v>3275.296348110883</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2820.330162583948</v>
+        <v>2187.801065021919</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2903.88716527619</v>
+        <v>2485.744532929124</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3058.99814380203</v>
+        <v>2616.905171970499</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3187.531147187758</v>
+        <v>2714.736827673556</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3388.721821267638</v>
+        <v>2890.018024789376</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>53665852.43808047</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>67262230.00924896</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>91552316.1441844</v>
+        <v>78320979.07905748</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>105696187.4316451</v>
+        <v>90018675.68212724</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>106700901.0985345</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>2333.953299674143</v>
+        <v>1810.50629549707</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>2403.829909964542</v>
+        <v>2057.692574366109</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>2530.085840240638</v>
+        <v>2164.432408783949</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>2636.492151053575</v>
+        <v>2245.431341008889</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>2792.533749215437</v>
+        <v>2381.568418928617</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>2040.878803226025</v>
+        <v>1583.161035014337</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>2101.321035605943</v>
+        <v>1798.743194517216</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>2213.628355424478</v>
+        <v>1893.710038323504</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>2306.637641970869</v>
+        <v>1964.502891299138</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>2452.545577101909</v>
+        <v>2091.61486196898</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>69181528.77413526</v>
+        <v>53665852.43808047</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>78576830.33966155</v>
+        <v>67262230.00924896</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>91552316.1441844</v>
+        <v>78320979.07905748</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>105696187.4316451</v>
+        <v>90018675.68212724</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>125113292.9968061</v>
+        <v>106700901.0985345</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="AS13" s="154" t="n">
-        <v>0.9657</v>
+        <v>0.867</v>
       </c>
       <c r="AT13" s="154" t="n">
         <v>0.9340000000000001</v>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>638.7886600278505</v>
+        <v>463.3616461095109</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>693.6670163280271</v>
+        <v>598.8099518086739</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>759.4199686674209</v>
+        <v>655.132793588322</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>814.8034130925719</v>
+        <v>699.8729211623341</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>882.658470037088</v>
+        <v>759.204808869923</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>86.98175081777943</v>
+        <v>63.09443132358729</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>98.14608420420738</v>
+        <v>84.72487601275743</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>112.2459606771623</v>
+        <v>96.83180956707044</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>127.1173298495458</v>
+        <v>109.1870450499081</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>146.5055993898356</v>
+        <v>126.0144884560616</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>142518411.1355036</v>
+        <v>103379364.2826719</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>163445915.2361946</v>
+        <v>141095134.0082563</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>189842221.9364554</v>
+        <v>163772181.835676</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>187496412.7363419</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>256411098.5460379</v>
+        <v>220547975.9975475</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>694.4528293624943</v>
+        <v>503.7390709859865</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>752.7567050392141</v>
+        <v>649.8192874360767</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>822.3954565696355</v>
+        <v>709.4601868873959</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>880.7865644582514</v>
+        <v>756.548948964574</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>952.5167538995755</v>
+        <v>819.2923136616373</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>101.7930913716059</v>
+        <v>73.83821494023815</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>114.7743853696818</v>
+        <v>99.07930253899897</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>131.1455601554059</v>
+        <v>113.1360258304494</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>148.3622074838843</v>
+        <v>127.4352682786829</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>170.7832965679116</v>
+        <v>146.896568073004</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>142518411.1355036</v>
+        <v>103379364.2826719</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>163445915.2361946</v>
+        <v>141095134.0082563</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>189842221.9364554</v>
+        <v>163772181.835676</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>218286366.5970434</v>
+        <v>187496412.7363419</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>256411098.5460379</v>
+        <v>220547975.9975475</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>157692.5140852467</v>
       </c>
       <c r="D19" s="75" t="n">
-        <v>166487.4670031312</v>
+        <v>166487.4670031313</v>
       </c>
       <c r="E19" s="75" t="n">
         <v>176028.3867149508</v>
@@ -3208,7 +3208,7 @@
         <v>142125.3440195271</v>
       </c>
       <c r="V19" s="75" t="n">
-        <v>150270.1402658387</v>
+        <v>150270.1402658388</v>
       </c>
       <c r="W19" s="75" t="n">
         <v>160277.0827357595</v>
@@ -3415,7 +3415,7 @@
         <v>199453.1815695046</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>210389.4345210398</v>
+        <v>210389.4345210399</v>
       </c>
       <c r="F21" s="86" t="n">
         <v>224297.4352039117</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>9211.00494835728</v>
+        <v>9211.004948357282</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>9752.664248588851</v>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97222200886944</v>
+        <v>0.7755555</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.949877939943838</v>
+        <v>0.9390429845289819</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.943844334714395</v>
+        <v>0.932452822637531</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.932019789921236</v>
+        <v>0.9169535229557469</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.9296716375637419</v>
+        <v>0.916033288559604</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.949183430955845</v>
+        <v>0.943359124547455</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.9487365842958559</v>
+        <v>0.9440178219936239</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.947337586100609</v>
+        <v>0.943211670924014</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94373489701852</v>
+        <v>0.939015226182339</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.941703088585464</v>
+        <v>0.9372355209007139</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3756,7 +3756,7 @@
         <v>175582.683187578</v>
       </c>
       <c r="U23" s="86" t="n">
-        <v>184441.6209077879</v>
+        <v>184441.620907788</v>
       </c>
       <c r="V23" s="86" t="n">
         <v>194655.0944595704</v>
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.9722</v>
+        <v>0.857</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.9499</v>
+        <v>0.924</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.9438</v>
+        <v>0.9175</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.902</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.9297</v>
+        <v>0.901</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9492</v>
+        <v>0.9284</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.9487</v>
+        <v>0.9289999999999999</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9473</v>
+        <v>0.9282</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.9437</v>
+        <v>0.924</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.9417</v>
+        <v>0.9222</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -3843,7 +3843,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="D24" s="80" t="n">
-        <v>23768.57981326902</v>
+        <v>23768.57981326903</v>
       </c>
       <c r="E24" s="80" t="n">
         <v>26311.55657416943</v>
@@ -3870,7 +3870,7 @@
         <v>4343.01680614511</v>
       </c>
       <c r="M24" s="79" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="N24" s="80" t="n">
         <v>27059.18855224806</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="T24" s="79" t="n">
-        <v>29641.35091468801</v>
+        <v>29641.350914688</v>
       </c>
       <c r="U24" s="80" t="n">
         <v>32688.18231021205</v>
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>309.2209694257513</v>
+        <v>297.5317153231276</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>350.2537801471804</v>
+        <v>350.2537801471803</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>387.8149181787844</v>
+        <v>387.8149181787843</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>422.970205261525</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>459.4487048068605</v>
+        <v>459.4487048068604</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>38.6286882942305</v>
+        <v>37.16843624870832</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>45.44826524829606</v>
@@ -4438,7 +4438,7 @@
         <v>69.20346589917969</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.2093999</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>58312864.66497567</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>362.2254447234465</v>
+        <v>348.5325012155357</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>410.2918101430514</v>
+        <v>410.2918101430513</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>454.2914132523853</v>
+        <v>454.2914132523852</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>495.4727714299193</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>538.2041578077307</v>
+        <v>538.2041578077306</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>47.57456853187856</v>
+        <v>45.77614191991703</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>55.95758340650233</v>
@@ -4488,7 +4488,7 @@
         <v>85.10166208170702</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.2093999</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>58312864.66497567</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>565.9086046083704</v>
+        <v>549.6518846949791</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>638.8115762007227</v>
@@ -4525,7 +4525,7 @@
         <v>817.4262300366823</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>64.2268940149862</v>
+        <v>62.38186353054735</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>73.73722693051934</v>
@@ -4540,7 +4540,7 @@
         <v>109.5986592243839</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="N36" s="159" t="n">
         <v>21058880.08272808</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>572.8965559382135</v>
+        <v>556.4390948333779</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>646.6997478367067</v>
@@ -4575,7 +4575,7 @@
         <v>827.5199707303525</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>64.51215749937907</v>
+        <v>62.65893231966694</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>74.06599340112449</v>
@@ -4590,7 +4590,7 @@
         <v>110.105408957194</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="AE36" s="159" t="n">
         <v>21058880.08272808</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>352.6872406269886</v>
+        <v>340.2245534468738</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>397.9467468160924</v>
+        <v>397.9467468160923</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>439.6837884462557</v>
@@ -4624,10 +4624,10 @@
         <v>478.0091880397895</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>517.7313269920801</v>
+        <v>517.73132699208</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>43.31988792890257</v>
+        <v>41.78912029757072</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>50.59863425201017</v>
@@ -4642,7 +4642,7 @@
         <v>76.44629685405459</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>66953773.24032705</v>
+        <v>64587869.8695696</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>79371744.74770375</v>
@@ -4662,25 +4662,25 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>402.4349213094808</v>
+        <v>388.2143316286122</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>454.3604030021783</v>
+        <v>454.3604030021781</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>502.1648440216011</v>
+        <v>502.164844021601</v>
       </c>
       <c r="W37" s="162" t="n">
         <v>545.9684251056387</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>591.3495216092394</v>
+        <v>591.3495216092393</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>51.22909120227973</v>
+        <v>49.41884102980234</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>59.83923779340303</v>
+        <v>59.83923779340302</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>68.78340346017796</v>
@@ -4692,7 +4692,7 @@
         <v>90.37740666187939</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>66953773.24032705</v>
+        <v>64587869.8695696</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>79371744.74770375</v>
@@ -4714,22 +4714,22 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>722.1068685387845</v>
+        <v>702.8801848671825</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>802.3898184552372</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>873.7820185630104</v>
+        <v>873.7820185630105</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236424</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>998.5916384034792</v>
+        <v>998.5916384034794</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>123.6967833481126</v>
+        <v>120.4032557163351</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>142.9612665200117</v>
@@ -4744,7 +4744,7 @@
         <v>213.9019892506383</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597154</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>9952954.78023549</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>918.4273843373522</v>
+        <v>893.9735069912974</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1020.537006764651</v>
@@ -4776,10 +4776,10 @@
         <v>1192.810801315761</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1270.080574549747</v>
+        <v>1270.080574549748</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>142.8192037262081</v>
+        <v>139.0165260729262</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>165.188071529187</v>
@@ -4788,13 +4788,13 @@
         <v>189.2064298013173</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>216.7744626508145</v>
+        <v>216.7744626508146</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>248.1540168809688</v>
+        <v>248.1540168809689</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597154</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>9952954.78023549</v>
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>374.1595403752355</v>
+        <v>361.3036998562408</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>421.626684031425</v>
+        <v>421.6266840314249</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>465.4616512575342</v>
+        <v>465.4616512575341</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>505.845018512008</v>
@@ -4831,7 +4831,7 @@
         <v>547.4226098276001</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>46.7257947750164</v>
+        <v>45.12033159439441</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>54.52366849543231</v>
@@ -4846,7 +4846,7 @@
         <v>82.41128841210249</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>75413412.42216523</v>
+        <v>72822264.26616675</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>89324699.52793925</v>
@@ -4866,22 +4866,22 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>429.5037019203071</v>
+        <v>414.7462776176479</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>484.2979534028133</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>534.8463416171079</v>
+        <v>534.8463416171078</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>581.350465362641</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>629.2240266740072</v>
+        <v>629.2240266740071</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>55.20014184925166</v>
+        <v>53.30350647406336</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>64.41675924257736</v>
@@ -4896,7 +4896,7 @@
         <v>97.34893054490384</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>75413412.42216523</v>
+        <v>72822264.26616675</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>89324699.52793925</v>
@@ -4921,46 +4921,46 @@
         <v>3301.597169367806</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3686.742635471712</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437094</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>2900.977332425373</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4971,46 +4971,46 @@
         <v>2400.692552637465</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>2530.613654031521</v>
+        <v>2530.61365403152</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>2680.743632380418</v>
+        <v>2680.743632380417</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>2828.85423932787</v>
+        <v>2828.854239327869</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>3003.693394875161</v>
+        <v>3003.69339487516</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>2099.237608749254</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>2212.149737452303</v>
+        <v>2212.149737452302</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>2345.442207485143</v>
+        <v>2345.442207485142</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>2474.933092243421</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>2637.996748523081</v>
+        <v>2637.99674852308</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>656.9627481758932</v>
+        <v>645.3488377672923</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>730.1653162186614</v>
+        <v>730.1653162186611</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>804.512124264402</v>
+        <v>804.5121242644018</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>874.124505895719</v>
+        <v>874.1245058957189</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>949.2839689357262</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>89.45645662511873</v>
+        <v>87.87502864370011</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>103.3101833037134</v>
@@ -5050,16 +5050,16 @@
         <v>157.564246626724</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>146573182.8131704</v>
+        <v>143982034.6571719</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="O41" s="183" t="n">
         <v>201114502.5764502</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>275765716.3780742</v>
@@ -5070,22 +5070,22 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>714.2106111223355</v>
+        <v>701.5846622789983</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>792.3640949229716</v>
+        <v>792.3640949229713</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>871.2269140238819</v>
+        <v>871.2269140238817</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>944.911506365014</v>
+        <v>944.9115063650139</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1024.415348987214</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>104.689192588194</v>
+        <v>102.8384774497116</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>120.8134067421567</v>
@@ -5100,16 +5100,16 @@
         <v>183.6744914339316</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>146573182.8131704</v>
+        <v>143982034.6571719</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="AF41" s="189" t="n">
         <v>201114502.5764502</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>275765716.3780742</v>
@@ -5374,7 +5374,7 @@
         <v>0.1029411561032852</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1178983509663407</v>
+        <v>0.1178983509663406</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.134965310654519</v>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.08730521334694913</v>
+        <v>0.08730521334694911</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1001953601886124</v>
+        <v>0.1001953601886123</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1146899651281048</v>
@@ -5637,7 +5637,7 @@
         <v>0.1483272616838144</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.1662563205568682</v>
+        <v>0.1662563205568681</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.01268139649462298</v>
@@ -5680,10 +5680,10 @@
         <v>0.05511847987654938</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.06002765782677747</v>
+        <v>0.06002765782677748</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.06501912662649771</v>
+        <v>0.06501912662649773</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.06957975474179512</v>
@@ -5692,13 +5692,13 @@
         <v>0.07390165411824727</v>
       </c>
       <c r="H49" s="155" t="n">
-        <v>0.009441786196499305</v>
+        <v>0.009441786196499307</v>
       </c>
       <c r="I49" s="156" t="n">
         <v>0.01069508833707209</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.01217239558540951</v>
+        <v>0.01217239558540952</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.01388566074660945</v>
@@ -5707,13 +5707,13 @@
         <v>0.01583000519619676</v>
       </c>
       <c r="M49" s="158" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="N49" s="159" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>863.5965974050195</v>
+        <v>863.5965974050197</v>
       </c>
       <c r="P49" s="159" t="n">
         <v>1005.619876619043</v>
@@ -5730,10 +5730,10 @@
         <v>0.07010364186689812</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.07634748701020522</v>
+        <v>0.07634748701020523</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.0826959955668474</v>
+        <v>0.08269599556684742</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.08849652999375823</v>
@@ -5757,13 +5757,13 @@
         <v>0.01836485668246825</v>
       </c>
       <c r="AD49" s="158" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="AE49" s="159" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>863.5965974050195</v>
+        <v>863.5965974050197</v>
       </c>
       <c r="AG49" s="159" t="n">
         <v>1005.619876619043</v>
@@ -5782,7 +5782,7 @@
         <v>0.08543437829440997</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.09784356153829186</v>
+        <v>0.09784356153829184</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.1117403837389542</v>
@@ -5835,7 +5835,7 @@
         <v>0.1123871861087075</v>
       </c>
       <c r="V50" s="162" t="n">
-        <v>0.1283971199178443</v>
+        <v>0.1283971199178442</v>
       </c>
       <c r="W50" s="162" t="n">
         <v>0.1450545426488207</v>
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>0.07718104575580054</v>
+        <v>0.07718104575580055</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.08797366820908514</v>
+        <v>0.08797366820908513</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.09997933894145931</v>
+        <v>0.0999793389414593</v>
       </c>
       <c r="F52" s="180" t="n">
         <v>0.1124814121024787</v>
@@ -6036,7 +6036,7 @@
         <v>0.08390661724635966</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.09546766251311567</v>
+        <v>0.09546766251311566</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.1082702029031056</v>
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.006733567703092374</v>
+        <v>0.00676051474070819</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.006312652989907675</v>
+        <v>0.006312652989907674</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.005913511288780401</v>
+        <v>0.0059135112887804</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002182438534425571</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008411748025817799</v>
+        <v>0.000844541096654421</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.0008191178618692286</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>1050.977606359472</v>
@@ -6384,13 +6384,13 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.007887788335822189</v>
+        <v>0.007919354444364229</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.007394723394407928</v>
+        <v>0.007394723394407926</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.006927163641047748</v>
+        <v>0.006927163641047746</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0002556536738701703</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.001035979476908445</v>
+        <v>0.001040125359026872</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.001008528176485717</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>1050.977606359472</v>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.005593337166758679</v>
+        <v>0.005615721120358992</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.005269294769275123</v>
+        <v>0.005269294769275122</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.004947709728648776</v>
+        <v>0.004947709728648775</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0001826834310492176</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0006870187273625166</v>
+        <v>0.0006897681048552988</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.0006699869289792132</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>1050.977606359472</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.006382295539130637</v>
+        <v>0.006407836822080718</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.006016279600374656</v>
+        <v>0.006016279600374655</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.005650801665740215</v>
+        <v>0.005650801665740214</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002086557908057063</v>
@@ -6603,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008124523567441308</v>
+        <v>0.0008157037065758386</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0007923436621229795</v>
+        <v>0.0007923436621229794</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.0007740115133016669</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>1050.977606359472</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.005268227716249654</v>
+        <v>0.005289310615642388</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.004960780226548962</v>
+        <v>0.00496078022654896</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.004653902074605053</v>
+        <v>0.004653902074605052</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0001716246726630459</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006579068566597677</v>
+        <v>0.0006605397314738091</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.0006415152237634267</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>1050.977606359472</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.006047482591033658</v>
+        <v>0.006071683987388035</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.005698158589079581</v>
+        <v>0.00569815858907958</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.005347642479508114</v>
+        <v>0.005347642479508113</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0001972423957319334</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0007772270538377742</v>
+        <v>0.0007803374356708963</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.0007579154679050752</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>1050.977606359472</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.00475929400479345</v>
+        <v>0.004778340204405136</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.004460365371489599</v>
+        <v>0.004460365371489598</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0.004164063495649975</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006480574109995107</v>
+        <v>0.0006506508693564218</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.0006310915540558638</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>1050.977606359472</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.005174019819407359</v>
+        <v>0.005194725708595124</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.004840319434657629</v>
+        <v>0.004840319434657628</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0.004509371679676935</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007584092827714781</v>
+        <v>0.0007614443578419554</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007380136030496262</v>
+        <v>0.0007380136030496261</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.0007190993945259967</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>1050.977606359472</v>
@@ -7297,28 +7297,28 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.002858008376089823</v>
+        <v>0.002869445828360696</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.00423130770579009</v>
+        <v>0.004231307705790089</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.005664116158427144</v>
+        <v>0.005664116158427142</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.007022073357940789</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.008333118956914248</v>
+        <v>0.008333118956914246</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003570298447330322</v>
+        <v>0.0003584586410383803</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>0.0005490464510592812</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007655346816305535</v>
+        <v>0.0007655346816305533</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.0009978984895167369</v>
@@ -7327,13 +7327,13 @@
         <v>0.001255157991600049</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>450.6865261022974</v>
+        <v>452.4901267056214</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>704.4597020478225</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>997.0452295340147</v>
+        <v>997.0452295340144</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1318.398827527651</v>
@@ -7347,28 +7347,28 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.003347907992705033</v>
+        <v>0.003361305972289063</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.004956608597204411</v>
+        <v>0.00495660859720441</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.006635018958325118</v>
+        <v>0.006635018958325115</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.008225747593005714</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.00976152337180492</v>
+        <v>0.009761523371804918</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004397131139116242</v>
+        <v>0.0004414728000606627</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.0006760062768368415</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009422561473262581</v>
+        <v>0.0009422561473262579</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.001227759612287847</v>
@@ -7377,13 +7377,13 @@
         <v>0.001543506959838086</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>450.6865261022974</v>
+        <v>452.4901267056214</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>704.4597020478225</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>997.0452295340147</v>
+        <v>997.0452295340144</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1318.398827527651</v>
@@ -7501,28 +7501,28 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.002374046742791253</v>
+        <v>0.002383547430940615</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.003531955201237717</v>
+        <v>0.003531955201237716</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.004739046101834101</v>
+        <v>0.0047390461018341</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>0.005877904160290901</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.006976396845718804</v>
+        <v>0.006976396845718802</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0002915995448342947</v>
+        <v>0.0002927664958845969</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.0004490854890805339</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006269030858094164</v>
+        <v>0.0006269030858094163</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>0.0008180565418405473</v>
@@ -7531,13 +7531,13 @@
         <v>0.001030109009122541</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>450.6865261022974</v>
+        <v>452.4901267056214</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>704.4597020478225</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>997.0452295340147</v>
+        <v>997.0452295340144</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1318.398827527651</v>
@@ -7551,28 +7551,28 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.002708913745849634</v>
+        <v>0.002719754536917033</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.004032651608436553</v>
+        <v>0.004032651608436552</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.005412485993509829</v>
+        <v>0.005412485993509827</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.006713574043369173</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.007968397356289647</v>
+        <v>0.007968397356289646</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003448388347951521</v>
+        <v>0.0003462188439466681</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005310999746912964</v>
+        <v>0.0005310999746912963</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007413685212064236</v>
+        <v>0.0007413685212064235</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.000967307747289834</v>
@@ -7581,13 +7581,13 @@
         <v>0.00121782983159106</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>450.6865261022974</v>
+        <v>452.4901267056214</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>704.4597020478225</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>997.0452295340147</v>
+        <v>997.0452295340144</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1318.398827527651</v>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.006483527712111256</v>
+        <v>0.006495048561595429</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.009695372243502838</v>
+        <v>0.00969537224350284</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.01299893853538077</v>
@@ -7618,22 +7618,22 @@
         <v>0.01902315707875442</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001110627190625365</v>
+        <v>0.001112600710175891</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001727418099574823</v>
+        <v>0.001727418099574824</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248186</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.004074829975022104</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925453</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7642,7 +7642,7 @@
         <v>172.6544121934863</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>302.956044420873</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.008246216255999028</v>
+        <v>0.008260869299915511</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.012331270837786</v>
@@ -7662,13 +7662,13 @@
         <v>0.01653298374293271</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02048588172280477</v>
+        <v>0.02048588172280478</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>0.02419501760595788</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001282320256909174</v>
+        <v>0.001284598864995134</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.001995987245632264</v>
@@ -7677,13 +7677,13 @@
         <v>0.00281475551022546</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003722984397433852</v>
+        <v>0.003722984397433853</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>0.004727330633769202</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925453</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2627442393418</v>
@@ -7692,7 +7692,7 @@
         <v>172.6544121934863</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>302.956044420873</v>
@@ -7705,22 +7705,22 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.002612907919934834</v>
+        <v>0.002622526028779913</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.003892820150663699</v>
+        <v>0.003892820150663698</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.005229539633518428</v>
+        <v>0.005229539633518427</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.006497115909970409</v>
+        <v>0.006497115909970411</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.007720238158554332</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003263051881837591</v>
+        <v>0.000327506316931053</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005034093985173547</v>
@@ -7729,13 +7729,13 @@
         <v>0.0007040544210179799</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.000921108474279071</v>
+        <v>0.0009211084742790711</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.001162236930065986</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>526.6424648415287</v>
+        <v>528.5810347048759</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>824.7224462871643</v>
@@ -7755,22 +7755,22 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.002999398660965373</v>
+        <v>0.00301043944145781</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.004471455207496178</v>
+        <v>0.004471455207496177</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.006009088254150194</v>
+        <v>0.006009088254150193</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.007466914211959673</v>
+        <v>0.007466914211959674</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.008873874140013571</v>
+        <v>0.008873874140013569</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0003854849930454487</v>
+        <v>0.0003869039625364778</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.0005947509204641971</v>
@@ -7785,7 +7785,7 @@
         <v>0.001372900780484587</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>526.6424648415287</v>
+        <v>528.5810347048759</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>824.7224462871643</v>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.002360489650070751</v>
+        <v>0.002369178607767597</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.003500134939365452</v>
@@ -7918,13 +7918,13 @@
         <v>0.004679113298454359</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.00579016030296049</v>
+        <v>0.005790160302960491</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.006854465118683069</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003214201118433282</v>
+        <v>0.0003226032586343502</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.0004952297433767576</v>
@@ -7933,13 +7933,13 @@
         <v>0.0006915956769268278</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009033218384782984</v>
+        <v>0.0009033218384782986</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001137719236600299</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>526.6424648415287</v>
+        <v>528.5810347048759</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>824.7224462871643</v>
@@ -7959,25 +7959,25 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.002566183181932265</v>
+        <v>0.002575629297109892</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.003798292238395006</v>
+        <v>0.003798292238395005</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.005067132385491233</v>
+        <v>0.005067132385491232</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.006259050120507664</v>
+        <v>0.006259050120507666</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.007396963929085195</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003761518537616274</v>
+        <v>0.0003775364679855562</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.000579133542348865</v>
+        <v>0.0005791335423488649</v>
       </c>
       <c r="AA74" s="186" t="n">
         <v>0.00080804424412646</v>
@@ -7989,7 +7989,7 @@
         <v>0.00132625266614081</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>526.6424648415287</v>
+        <v>528.5810347048759</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>824.7224462871643</v>
@@ -8260,22 +8260,22 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>309.3335021579338</v>
+        <v>297.6442864398</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>350.3822224588424</v>
+        <v>350.3822224588423</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>387.9614611168861</v>
+        <v>387.961461116886</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>423.130517841733</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>459.6288996629908</v>
+        <v>459.6288996629907</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>38.64274617601791</v>
+        <v>37.1824989255861</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>45.46493167869708</v>
@@ -8290,7 +8290,7 @@
         <v>69.23060735904443</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>48779577.64607865</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>58334248.7001003</v>
@@ -8310,22 +8310,22 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>362.3572670220327</v>
+        <v>348.6643684782099</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>410.4422691289004</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>454.4630755462574</v>
+        <v>454.4630755462573</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>495.6605636607258</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>538.4152403938176</v>
+        <v>538.4152403938175</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>47.59188202840254</v>
+        <v>45.79346132200928</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>55.97810373140712</v>
@@ -8340,7 +8340,7 @@
         <v>85.13503878207602</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>48779577.64607865</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>58334248.7001003</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>565.9192085784429</v>
+        <v>549.6624886650516</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>638.8223657606205</v>
@@ -8377,7 +8377,7 @@
         <v>817.436536358424</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>64.22809749564799</v>
+        <v>62.38306701120914</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>73.73847235601929</v>
@@ -8392,7 +8392,7 @@
         <v>109.6000410726815</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>21059235.76827997</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>572.9072908482049</v>
+        <v>556.4498297433693</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>646.7106706282233</v>
@@ -8427,7 +8427,7 @@
         <v>827.5304043165925</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>64.51336632529524</v>
+        <v>62.6601411455831</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>74.06724437950679</v>
@@ -8442,7 +8442,7 @@
         <v>110.1067971947236</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>21059235.76827997</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>352.7825132242452</v>
+        <v>340.319857928772</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>398.0557434262515</v>
@@ -8476,10 +8476,10 @@
         <v>478.1451129027882</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>517.8838621529347</v>
+        <v>517.8838621529346</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>43.33159007675604</v>
+        <v>41.80082636175272</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>50.61249309030016</v>
@@ -8494,7 +8494,7 @@
         <v>76.46881963291582</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>66971859.68956006</v>
+        <v>64605962.37174931</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>79393484.46838027</v>
@@ -8514,25 +8514,25 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>402.543632415989</v>
+        <v>388.3230791171944</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>454.4848511704671</v>
+        <v>454.484851170467</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>502.3068952373187</v>
+        <v>502.3068952373185</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>546.1236745971567</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>591.5237463271526</v>
+        <v>591.5237463271525</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>51.24292988996589</v>
+        <v>49.43268434884748</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>59.8556276096942</v>
+        <v>59.85562760969419</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>68.80286074835541</v>
@@ -8544,7 +8544,7 @@
         <v>90.40403385545272</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>66971859.68956006</v>
+        <v>64605962.37174931</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>79393484.46838027</v>
@@ -8566,22 +8566,22 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>722.1684705463732</v>
+        <v>702.9417983956207</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>802.4595414853076</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>873.8600366281722</v>
+        <v>873.8600366281723</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542814</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>998.6845632146762</v>
+        <v>998.6845632146764</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>123.7073357614998</v>
+        <v>120.4138101032418</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>142.9736890264484</v>
@@ -8590,19 +8590,19 @@
         <v>163.5975535817733</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>187.1765979516572</v>
+        <v>187.1765979516573</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>213.9218940858095</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497286</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>9953819.634386763</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>11606777.78056714</v>
+        <v>11606777.78056715</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>13555603.20628449</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>918.5057341954752</v>
+        <v>894.0518715024642</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>1020.625685522499</v>
@@ -8631,13 +8631,13 @@
         <v>1270.198762999416</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>142.8313874486668</v>
+        <v>139.0287120739929</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>165.2024254163047</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>189.2233236252409</v>
+        <v>189.223323625241</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>216.7942684772811</v>
@@ -8646,13 +8646,13 @@
         <v>248.1771090682851</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497286</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>9953819.634386763</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>11606777.78056714</v>
+        <v>11606777.78056715</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>13555603.20628449</v>
@@ -8668,13 +8668,13 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>374.2528558891661</v>
+        <v>361.3970460711797</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>421.7333811933404</v>
+        <v>421.7333811933403</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>465.5832750829812</v>
+        <v>465.5832750829813</v>
       </c>
       <c r="F83" s="162" t="n">
         <v>505.9779021989668</v>
@@ -8683,13 +8683,13 @@
         <v>547.5714642776338</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>46.73744820378872</v>
+        <v>45.13198885717029</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>54.53746629549101</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>62.68160988267767</v>
+        <v>62.68160988267768</v>
       </c>
       <c r="K83" s="162" t="n">
         <v>71.73344911366031</v>
@@ -8698,13 +8698,13 @@
         <v>82.43369758335871</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>72841078.58424661</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>89347304.10276702</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>104137768.9478334</v>
+        <v>104137768.9478335</v>
       </c>
       <c r="P83" s="165" t="n">
         <v>120802325.6856647</v>
@@ -8718,28 +8718,28 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>429.6108202865516</v>
+        <v>414.8534312260693</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>484.4205102027185</v>
+        <v>484.4205102027184</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>534.9860954677594</v>
+        <v>534.9860954677595</v>
       </c>
       <c r="W83" s="162" t="n">
         <v>581.5031840618975</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>629.3951244598076</v>
+        <v>629.3951244598074</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>55.21390878300548</v>
+        <v>53.31727793716851</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>64.43306059553076</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>74.05561417149435</v>
+        <v>74.05561417149437</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>84.74475110704563</v>
@@ -8748,13 +8748,13 @@
         <v>97.37540154054319</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>75432220.55232911</v>
+        <v>72841078.58424661</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>89347304.10276702</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>104137768.9478334</v>
+        <v>104137768.9478335</v>
       </c>
       <c r="AG83" s="165" t="n">
         <v>120802325.6856647</v>
@@ -8773,46 +8773,46 @@
         <v>3301.597169367806</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3686.742635471712</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437094</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>2900.977332425373</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8823,46 +8823,46 @@
         <v>2400.692552637465</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>2530.613654031521</v>
+        <v>2530.61365403152</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>2680.743632380418</v>
+        <v>2680.743632380417</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>2828.85423932787</v>
+        <v>2828.854239327869</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>3003.693394875161</v>
+        <v>3003.69339487516</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>2099.237608749254</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>2212.149737452303</v>
+        <v>2212.149737452302</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>2345.442207485143</v>
+        <v>2345.442207485142</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>2474.933092243421</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>2637.996748523081</v>
+        <v>2637.99674852308</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,22 +8872,22 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>657.047049005304</v>
+        <v>645.4331663318602</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>730.2612503871811</v>
+        <v>730.261250387181</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>804.6209467801376</v>
+        <v>804.6209467801375</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>874.2429304181996</v>
+        <v>874.2429304181995</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>949.4161303554341</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>89.46793559178857</v>
+        <v>87.8865113869751</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>103.3237569100115</v>
@@ -8899,10 +8899,10 @@
         <v>136.3904779593478</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>157.5861830706237</v>
+        <v>157.5861830706236</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>172068464.5824612</v>
@@ -8922,22 +8922,22 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>714.3022579425832</v>
+        <v>701.6763392512504</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>792.4682011971576</v>
+        <v>792.4682011971574</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>871.3447607308502</v>
+        <v>871.3447607308501</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>945.0395209592429</v>
+        <v>945.0395209592427</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1024.557970364297</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>104.7026262049249</v>
+        <v>102.8519154861319</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>120.8292800429893</v>
@@ -8949,10 +8949,10 @@
         <v>159.1851592051295</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>183.700063004027</v>
+        <v>183.7000630040269</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>172068464.5824612</v>
@@ -9284,7 +9284,7 @@
         <v>157692.5140852467</v>
       </c>
       <c r="D90" s="75" t="n">
-        <v>166487.4670031312</v>
+        <v>166487.4670031313</v>
       </c>
       <c r="E90" s="75" t="n">
         <v>176028.3867149508</v>
@@ -9337,7 +9337,7 @@
         <v>142125.3440195271</v>
       </c>
       <c r="V90" s="75" t="n">
-        <v>150270.1402658387</v>
+        <v>150270.1402658388</v>
       </c>
       <c r="W90" s="75" t="n">
         <v>160277.0827357595</v>
@@ -9530,7 +9530,7 @@
         <v>199453.1815695046</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>210389.4345210398</v>
+        <v>210389.4345210399</v>
       </c>
       <c r="F92" s="86" t="n">
         <v>224297.4352039117</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>9211.00494835728</v>
+        <v>9211.004948357282</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>9752.664248588851</v>
@@ -9809,7 +9809,7 @@
         <v>175582.683187578</v>
       </c>
       <c r="U94" s="86" t="n">
-        <v>184441.6209077879</v>
+        <v>184441.620907788</v>
       </c>
       <c r="V94" s="86" t="n">
         <v>194655.0944595704</v>
@@ -9871,7 +9871,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="D95" s="80" t="n">
-        <v>23768.57981326902</v>
+        <v>23768.57981326903</v>
       </c>
       <c r="E95" s="80" t="n">
         <v>26311.55657416943</v>
@@ -9898,7 +9898,7 @@
         <v>4343.01680614511</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="N95" s="80" t="n">
         <v>27059.18855224806</v>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="T95" s="79" t="n">
-        <v>29641.35091468801</v>
+        <v>29641.350914688</v>
       </c>
       <c r="U95" s="80" t="n">
         <v>32688.18231021205</v>
